--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -68724,13 +68724,13 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O369" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R369" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
@@ -69233,12 +69233,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -69272,81 +69272,100 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O372" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R372" t="n">
-        <v>0.05214830935724275</v>
+        <v>0.03737952171313338</v>
       </c>
       <c r="S372" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ372" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR372" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS372" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -69373,17 +69392,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -69408,7 +69427,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -69417,81 +69436,175 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O373" t="n">
-        <v>3</v>
-      </c>
-      <c r="R373" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S373" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ373" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK373" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM373" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN373" t="b">
+        <v>1</v>
       </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ373" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR373" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -69523,12 +69636,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -69553,7 +69666,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -69562,93 +69675,81 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="O374" t="n">
-        <v>100</v>
-      </c>
-      <c r="P374" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="R374" t="n">
-        <v>1.693265755097047</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA374" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO374" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ374" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS374" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR374" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr"/>
       <c r="AT374" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -69675,17 +69776,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -69719,173 +69820,81 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="O375" t="n">
-        <v>100</v>
-      </c>
-      <c r="P375" t="n">
-        <v>100</v>
-      </c>
-      <c r="U375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W375" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X375" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y375" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA375" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB375" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD375" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE375" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF375" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG375" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH375" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI375" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ375" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK375" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM375" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN375" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R375" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ375" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR375" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr"/>
       <c r="AT375" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69921,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -69956,106 +69965,26 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O376" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="P376" t="n">
-        <v>1</v>
-      </c>
-      <c r="U376" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W376" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X376" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y376" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>100</v>
+      </c>
+      <c r="R376" t="n">
+        <v>1.693265755097047</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB376" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC376" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD376" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE376" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF376" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG376" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH376" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI376" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ376" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK376" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM376" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN376" t="b">
-        <v>0</v>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
@@ -70149,17 +70078,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -70184,7 +70113,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -70193,81 +70122,173 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="O377" t="n">
-        <v>8</v>
-      </c>
-      <c r="R377" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="P377" t="n">
+        <v>100</v>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ377" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK377" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM377" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN377" t="b">
+        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR377" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS377" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ377" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT377" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70294,7 +70315,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -70329,7 +70350,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -70338,26 +70359,106 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="O378" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="P378" t="n">
-        <v>93</v>
-      </c>
-      <c r="R378" t="n">
-        <v>1.574737152240254</v>
-      </c>
-      <c r="S378" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF378" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG378" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ378" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK378" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM378" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN378" t="b">
+        <v>0</v>
       </c>
       <c r="AO378" t="inlineStr">
         <is>
@@ -70451,17 +70552,17 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -70495,173 +70596,81 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="O379" t="n">
-        <v>93</v>
-      </c>
-      <c r="P379" t="n">
-        <v>93</v>
-      </c>
-      <c r="U379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W379" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X379" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y379" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA379" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB379" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC379" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD379" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE379" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF379" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG379" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH379" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI379" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ379" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK379" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM379" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN379" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP379" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ379" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR379" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS379" t="inlineStr"/>
       <c r="AT379" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70688,7 +70697,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -70732,106 +70741,26 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="O380" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="P380" t="n">
-        <v>2</v>
-      </c>
-      <c r="U380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W380" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X380" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y380" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z380" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>93</v>
+      </c>
+      <c r="R380" t="n">
+        <v>1.574737152240254</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB380" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC380" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD380" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE380" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF380" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG380" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH380" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI380" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ380" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK380" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM380" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN380" t="b">
-        <v>0</v>
       </c>
       <c r="AO380" t="inlineStr">
         <is>
@@ -70925,17 +70854,17 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -70960,7 +70889,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -70969,81 +70898,173 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="O381" t="n">
-        <v>7</v>
-      </c>
-      <c r="R381" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S381" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>93</v>
+      </c>
+      <c r="P381" t="n">
+        <v>93</v>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF381" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG381" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ381" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK381" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM381" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN381" t="b">
+        <v>1</v>
       </c>
       <c r="AO381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR381" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS381" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ381" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT381" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71070,7 +71091,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -71105,7 +71126,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -71114,26 +71135,106 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="O382" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="P382" t="n">
-        <v>103</v>
-      </c>
-      <c r="R382" t="n">
-        <v>1.744063727749959</v>
-      </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF382" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG382" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH382" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI382" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ382" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK382" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM382" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN382" t="b">
+        <v>0</v>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
@@ -71227,17 +71328,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -71271,173 +71372,81 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="O383" t="n">
-        <v>103</v>
-      </c>
-      <c r="P383" t="n">
-        <v>103</v>
-      </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W383" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X383" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y383" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z383" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA383" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB383" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC383" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD383" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE383" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF383" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG383" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH383" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI383" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ383" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK383" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM383" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN383" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ383" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr"/>
       <c r="AT383" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71464,7 +71473,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -71508,106 +71517,26 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="O384" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="P384" t="n">
-        <v>1</v>
-      </c>
-      <c r="U384" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V384" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W384" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X384" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y384" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z384" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>103</v>
+      </c>
+      <c r="R384" t="n">
+        <v>1.744063727749959</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB384" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC384" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD384" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE384" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF384" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG384" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH384" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI384" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ384" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK384" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM384" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN384" t="b">
-        <v>0</v>
       </c>
       <c r="AO384" t="inlineStr">
         <is>
@@ -71701,17 +71630,17 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -71736,7 +71665,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -71745,81 +71674,173 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="O385" t="n">
-        <v>8</v>
-      </c>
-      <c r="R385" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S385" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="P385" t="n">
+        <v>103</v>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF385" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG385" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH385" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI385" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ385" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK385" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM385" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN385" t="b">
+        <v>1</v>
       </c>
       <c r="AO385" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP385" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR385" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS385" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ385" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS385" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT385" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU385" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV385" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW385" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ385" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA385" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB385" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC385" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71846,7 +71867,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -71881,7 +71902,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -71890,26 +71911,106 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="O386" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="P386" t="n">
-        <v>88</v>
-      </c>
-      <c r="R386" t="n">
-        <v>1.490073864485402</v>
-      </c>
-      <c r="S386" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF386" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ386" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK386" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM386" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN386" t="b">
+        <v>0</v>
       </c>
       <c r="AO386" t="inlineStr">
         <is>
@@ -72003,17 +72104,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -72047,173 +72148,81 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="O387" t="n">
-        <v>88</v>
-      </c>
-      <c r="P387" t="n">
-        <v>88</v>
-      </c>
-      <c r="U387" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V387" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W387" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X387" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y387" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z387" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA387" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB387" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC387" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD387" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE387" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF387" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG387" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH387" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI387" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ387" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK387" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM387" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN387" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R387" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO387" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP387" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ387" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS387" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR387" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr"/>
       <c r="AT387" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU387" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV387" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA387" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB387" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC387" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -72240,7 +72249,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -72284,106 +72293,26 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="O388" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="P388" t="n">
-        <v>0</v>
-      </c>
-      <c r="U388" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V388" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W388" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X388" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y388" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z388" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>88</v>
+      </c>
+      <c r="R388" t="n">
+        <v>1.490073864485402</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB388" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC388" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD388" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE388" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF388" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG388" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH388" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI388" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ388" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK388" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM388" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN388" t="b">
-        <v>0</v>
       </c>
       <c r="AO388" t="inlineStr">
         <is>
@@ -72477,17 +72406,17 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -72512,90 +72441,182 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N389" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="O389" t="n">
-        <v>0</v>
-      </c>
-      <c r="R389" t="n">
-        <v>0</v>
-      </c>
-      <c r="S389" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>88</v>
+      </c>
+      <c r="P389" t="n">
+        <v>88</v>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF389" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ389" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK389" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM389" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN389" t="b">
+        <v>1</v>
       </c>
       <c r="AO389" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP389" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR389" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS389" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ389" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT389" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU389" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV389" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW389" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ389" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA389" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB389" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC389" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -72622,17 +72643,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -72657,12 +72678,12 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N390" t="n">
@@ -72671,23 +72692,101 @@
       <c r="O390" t="n">
         <v>0</v>
       </c>
-      <c r="R390" t="n">
+      <c r="P390" t="n">
         <v>0</v>
       </c>
-      <c r="S390" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U390" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1910</t>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE390" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF390" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG390" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH390" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI390" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ390" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK390" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM390" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN390" t="b">
+        <v>0</v>
       </c>
       <c r="AO390" t="inlineStr">
         <is>
@@ -72696,70 +72795,65 @@
       </c>
       <c r="AP390" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ390" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR390" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS390" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1910</t>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
         </is>
       </c>
       <c r="AT390" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU390" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV390" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA390" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB390" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC390" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -72786,17 +72880,17 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -72835,170 +72929,76 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
-      <c r="U391" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="V391" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W391" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X391" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y391" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z391" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA391" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB391" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC391" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD391" t="inlineStr">
+      <c r="R391" t="n">
+        <v>0</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO391" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP391" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR391" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr"/>
+      <c r="AT391" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU391" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV391" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE391" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF391" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG391" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH391" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI391" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ391" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK391" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM391" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN391" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO391" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP391" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ391" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR391" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS391" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AT391" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU391" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV391" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ391" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA391" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB391" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC391" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -73030,12 +73030,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -73069,81 +73069,100 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R392" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP392" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ392" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR392" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS392" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT392" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU392" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV392" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA392" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB392" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC392" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -73170,17 +73189,17 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -73219,17 +73238,34 @@
       <c r="O393" t="n">
         <v>0</v>
       </c>
-      <c r="R393" t="n">
-        <v>0</v>
-      </c>
-      <c r="S393" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U393" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
@@ -73237,6 +73273,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB393" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC393" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD393" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE393" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF393" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG393" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH393" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI393" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ393" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK393" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM393" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN393" t="b">
+        <v>1</v>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -73249,7 +73343,7 @@
       </c>
       <c r="AQ393" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR393" t="inlineStr">
@@ -73259,7 +73353,7 @@
       </c>
       <c r="AS393" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
       <c r="AT393" t="n">
@@ -73267,47 +73361,47 @@
       </c>
       <c r="AU393" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV393" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY393" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ393" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA393" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB393" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC393" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -73334,217 +73428,526 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>4</v>
+      </c>
+      <c r="O394" t="n">
+        <v>4</v>
+      </c>
+      <c r="R394" t="n">
+        <v>0.007751879695168184</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO394" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP394" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR394" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr"/>
+      <c r="AT394" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU394" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV394" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW394" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX394" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY394" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA394" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB394" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC394" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
+      <c r="R395" t="n">
+        <v>0</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO395" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP395" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ395" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR395" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT395" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU395" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV395" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW395" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX395" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY395" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA395" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB395" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC395" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
+      <c r="F396" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
+      <c r="G396" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>D021</t>
-        </is>
-      </c>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr">
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
         <is>
           <t>登革热</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr">
+      <c r="K396" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
+      <c r="L396" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M394" t="inlineStr">
+      <c r="M396" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N394" t="n">
+      <c r="N396" t="n">
         <v>0</v>
       </c>
-      <c r="O394" t="n">
+      <c r="O396" t="n">
         <v>0</v>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="U396" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
+      <c r="V396" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="W394" t="inlineStr">
+      <c r="W396" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X394" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>Denguefeber</t>
         </is>
       </c>
-      <c r="Y394" t="inlineStr">
+      <c r="Y396" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z394" t="inlineStr">
+      <c r="Z396" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA394" t="inlineStr">
+      <c r="AA396" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB394" t="inlineStr">
+      <c r="AB396" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC394" t="inlineStr">
+      <c r="AC396" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD394" t="inlineStr">
+      <c r="AD396" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE394" t="inlineStr">
+      <c r="AE396" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF394" t="inlineStr">
+      <c r="AF396" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG394" t="inlineStr">
+      <c r="AG396" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH394" t="inlineStr">
+      <c r="AH396" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI394" t="inlineStr">
+      <c r="AI396" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ394" t="inlineStr">
+      <c r="AJ396" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK394" t="inlineStr">
+      <c r="AK396" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM394" t="inlineStr">
+      <c r="AM396" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN394" t="b">
+      <c r="AN396" t="b">
         <v>1</v>
       </c>
-      <c r="AO394" t="inlineStr">
+      <c r="AO396" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP394" t="inlineStr">
+      <c r="AP396" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ394" t="inlineStr">
+      <c r="AQ396" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR394" t="inlineStr">
+      <c r="AR396" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS394" t="inlineStr">
+      <c r="AS396" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="AT394" t="n">
+      <c r="AT396" t="n">
         <v>2</v>
       </c>
-      <c r="AU394" t="inlineStr">
+      <c r="AU396" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV394" t="inlineStr">
+      <c r="AV396" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW394" t="inlineStr">
+      <c r="AW396" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX394" t="inlineStr">
+      <c r="AX396" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY394" t="inlineStr">
+      <c r="AY396" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ394" t="inlineStr">
+      <c r="AZ396" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA394" t="inlineStr">
+      <c r="BA396" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB394" t="inlineStr">
+      <c r="BB396" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC394" t="inlineStr">
+      <c r="BC396" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -73666,7 +74069,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -73676,7 +74079,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -73696,7 +74099,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -73728,7 +74131,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>482788</v>
+        <v>482796</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -67037,13 +67037,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O358" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R358" t="n">
-        <v>0.1616037200588708</v>
+        <v>0.1358940373222322</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -72885,12 +72885,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -72915,22 +72915,22 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N391" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O391" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R391" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S391" t="inlineStr">
         <is>
@@ -72963,42 +72963,42 @@
       </c>
       <c r="AV391" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ391" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA391" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB391" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC391" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -73030,12 +73030,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -73082,87 +73082,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA392" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO392" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP392" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ392" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR392" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS392" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr"/>
       <c r="AT392" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU392" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV392" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA392" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB392" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC392" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -73189,7 +73170,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -73238,98 +73219,23 @@
       <c r="O393" t="n">
         <v>0</v>
       </c>
+      <c r="R393" t="n">
+        <v>0</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U393" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W393" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X393" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y393" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z393" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA393" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB393" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC393" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD393" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE393" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF393" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG393" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH393" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI393" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ393" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK393" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM393" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN393" t="b">
-        <v>1</v>
       </c>
       <c r="AO393" t="inlineStr">
         <is>
@@ -73428,17 +73334,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -73472,81 +73378,175 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O394" t="n">
-        <v>4</v>
-      </c>
-      <c r="R394" t="n">
-        <v>0.007751879695168184</v>
-      </c>
-      <c r="S394" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF394" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG394" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH394" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI394" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ394" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK394" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM394" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN394" t="b">
+        <v>1</v>
       </c>
       <c r="AO394" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP394" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ394" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR394" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS394" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT394" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU394" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV394" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA394" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB394" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC394" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -73578,12 +73578,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -73617,100 +73617,81 @@
         </is>
       </c>
       <c r="N395" t="n">
+        <v>5</v>
+      </c>
+      <c r="O395" t="n">
+        <v>5</v>
+      </c>
+      <c r="R395" t="n">
+        <v>0.009689849618960231</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO395" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP395" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR395" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr"/>
+      <c r="AT395" t="n">
         <v>0</v>
       </c>
-      <c r="O395" t="n">
-        <v>0</v>
-      </c>
-      <c r="R395" t="n">
-        <v>0</v>
-      </c>
-      <c r="S395" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U395" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA395" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO395" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP395" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ395" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR395" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS395" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT395" t="n">
-        <v>2</v>
-      </c>
       <c r="AU395" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV395" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ395" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA395" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB395" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC395" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -73737,7 +73718,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -73786,98 +73767,23 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
+      <c r="R396" t="n">
+        <v>0</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U396" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V396" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W396" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X396" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y396" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z396" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA396" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB396" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC396" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD396" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE396" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF396" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG396" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH396" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI396" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ396" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK396" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM396" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN396" t="b">
-        <v>1</v>
       </c>
       <c r="AO396" t="inlineStr">
         <is>
@@ -73948,6 +73854,245 @@
         </is>
       </c>
       <c r="BC396" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC397" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD397" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE397" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF397" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG397" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH397" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI397" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ397" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK397" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM397" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN397" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO397" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP397" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ397" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR397" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS397" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT397" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU397" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV397" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW397" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX397" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY397" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA397" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB397" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC397" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -74069,7 +74214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -74079,7 +74224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11">
@@ -74131,7 +74276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>482796</v>
+        <v>482794</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -62444,13 +62444,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O334" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R334" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
@@ -62608,10 +62608,10 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O335" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U335" t="inlineStr">
         <is>
@@ -67037,13 +67037,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="O358" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="R358" t="n">
-        <v>0.1358940373222322</v>
+        <v>0.2056774618931082</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -73617,13 +73617,13 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O395" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R395" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S395" t="inlineStr">
         <is>
@@ -73762,13 +73762,13 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R396" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
@@ -73926,10 +73926,10 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U397" t="inlineStr">
         <is>
@@ -74276,7 +74276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>482794</v>
+        <v>482817</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -58378,13 +58378,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>42567</v>
+        <v>41466</v>
       </c>
       <c r="O312" t="n">
-        <v>42567</v>
+        <v>41466</v>
       </c>
       <c r="R312" t="n">
-        <v>19.93185452196065</v>
+        <v>19.41631497656918</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -67037,13 +67037,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O358" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R358" t="n">
-        <v>0.2056774618931082</v>
+        <v>0.209350273712628</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -68176,13 +68176,13 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>37468</v>
+        <v>39979</v>
       </c>
       <c r="O366" t="n">
-        <v>37468</v>
+        <v>39979</v>
       </c>
       <c r="R366" t="n">
-        <v>17.54426492890788</v>
+        <v>18.7200322299778</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -68282,12 +68282,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -68321,100 +68321,84 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>3</v>
+        <v>836</v>
       </c>
       <c r="O367" t="n">
-        <v>3</v>
+        <v>836</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>0</v>
       </c>
       <c r="R367" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.05916849487200793</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA367" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO367" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ367" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR367" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS367" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr"/>
       <c r="AT367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -68441,7 +68425,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -68490,98 +68474,23 @@
       <c r="O368" t="n">
         <v>3</v>
       </c>
+      <c r="R368" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U368" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W368" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X368" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y368" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA368" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB368" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC368" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD368" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE368" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF368" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG368" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH368" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI368" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ368" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK368" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM368" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN368" t="b">
-        <v>1</v>
       </c>
       <c r="AO368" t="inlineStr">
         <is>
@@ -68680,17 +68589,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -68724,81 +68633,175 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O369" t="n">
-        <v>17</v>
-      </c>
-      <c r="R369" t="n">
-        <v>0.03294548870446478</v>
-      </c>
-      <c r="S369" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ369" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK369" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM369" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN369" t="b">
+        <v>1</v>
       </c>
       <c r="AO369" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ369" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR369" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT369" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -68830,12 +68833,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -68869,100 +68872,81 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O370" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R370" t="n">
-        <v>0.2122770990954608</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA370" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO370" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ370" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR370" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr"/>
       <c r="AT370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -68989,7 +68973,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -69038,98 +69022,23 @@
       <c r="O371" t="n">
         <v>12</v>
       </c>
+      <c r="R371" t="n">
+        <v>0.2122770990954608</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U371" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V371" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W371" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X371" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y371" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB371" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC371" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD371" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE371" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF371" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG371" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH371" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI371" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ371" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK371" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM371" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN371" t="b">
-        <v>1</v>
       </c>
       <c r="AO371" t="inlineStr">
         <is>
@@ -69228,17 +69137,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -69272,22 +69181,39 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O372" t="n">
-        <v>4</v>
-      </c>
-      <c r="R372" t="n">
-        <v>0.03737952171313338</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
       </c>
       <c r="U372" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -69295,6 +69221,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM372" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN372" t="b">
+        <v>1</v>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69317,7 +69301,7 @@
       </c>
       <c r="AS372" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
       <c r="AT372" t="n">
@@ -69330,42 +69314,42 @@
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -69392,7 +69376,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -69441,98 +69425,23 @@
       <c r="O373" t="n">
         <v>4</v>
       </c>
+      <c r="R373" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U373" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DENGUE</t>
         </is>
       </c>
-      <c r="V373" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
-        </is>
-      </c>
-      <c r="W373" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X373" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y373" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z373" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA373" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB373" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC373" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD373" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE373" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF373" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG373" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH373" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI373" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ373" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK373" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM373" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN373" t="b">
-        <v>1</v>
       </c>
       <c r="AO373" t="inlineStr">
         <is>
@@ -69631,17 +69540,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -69675,81 +69584,175 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O374" t="n">
-        <v>12</v>
-      </c>
-      <c r="R374" t="n">
-        <v>0.05214830935724275</v>
-      </c>
-      <c r="S374" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC374" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE374" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF374" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG374" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH374" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI374" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ374" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK374" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM374" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN374" t="b">
+        <v>1</v>
       </c>
       <c r="AO374" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ374" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR374" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS374" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT374" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -69781,12 +69784,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -69811,7 +69814,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -69820,13 +69823,13 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O375" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R375" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
@@ -69859,42 +69862,42 @@
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -69926,12 +69929,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -69965,93 +69968,81 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="O376" t="n">
-        <v>100</v>
-      </c>
-      <c r="P376" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="R376" t="n">
-        <v>1.693265755097047</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA376" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO376" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ376" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS376" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR376" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr"/>
       <c r="AT376" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70078,7 +70069,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -70130,98 +70121,18 @@
       <c r="P377" t="n">
         <v>100</v>
       </c>
-      <c r="U377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W377" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y377" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z377" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R377" t="n">
+        <v>1.693265755097047</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB377" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC377" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD377" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE377" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF377" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG377" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ377" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK377" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM377" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN377" t="b">
-        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
@@ -70359,106 +70270,106 @@
         </is>
       </c>
       <c r="N378" t="n">
+        <v>100</v>
+      </c>
+      <c r="O378" t="n">
+        <v>100</v>
+      </c>
+      <c r="P378" t="n">
+        <v>100</v>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF378" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG378" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ378" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK378" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM378" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN378" t="b">
         <v>1</v>
-      </c>
-      <c r="O378" t="n">
-        <v>1</v>
-      </c>
-      <c r="P378" t="n">
-        <v>1</v>
-      </c>
-      <c r="U378" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W378" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X378" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y378" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z378" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA378" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB378" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC378" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD378" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE378" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF378" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG378" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH378" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI378" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ378" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK378" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM378" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN378" t="b">
-        <v>0</v>
       </c>
       <c r="AO378" t="inlineStr">
         <is>
@@ -70552,17 +70463,17 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -70587,7 +70498,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -70596,81 +70507,173 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O379" t="n">
-        <v>8</v>
-      </c>
-      <c r="R379" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S379" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P379" t="n">
+        <v>1</v>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD379" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF379" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG379" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH379" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI379" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ379" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK379" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM379" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN379" t="b">
+        <v>0</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP379" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR379" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS379" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ379" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS379" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT379" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70702,12 +70705,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -70741,93 +70744,81 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="O380" t="n">
-        <v>93</v>
-      </c>
-      <c r="P380" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="R380" t="n">
-        <v>1.574737152240254</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA380" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO380" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ380" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR380" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr"/>
       <c r="AT380" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70854,7 +70845,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -70906,98 +70897,18 @@
       <c r="P381" t="n">
         <v>93</v>
       </c>
-      <c r="U381" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V381" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W381" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X381" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y381" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z381" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R381" t="n">
+        <v>1.574737152240254</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB381" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC381" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD381" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE381" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF381" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG381" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH381" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI381" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ381" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK381" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM381" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN381" t="b">
-        <v>1</v>
       </c>
       <c r="AO381" t="inlineStr">
         <is>
@@ -71135,22 +71046,22 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="O382" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="P382" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="U382" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="V382" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="W382" t="inlineStr">
@@ -71160,7 +71071,7 @@
       </c>
       <c r="X382" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="Y382" t="inlineStr">
@@ -71195,7 +71106,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -71234,7 +71145,7 @@
         </is>
       </c>
       <c r="AN382" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
@@ -71328,17 +71239,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -71363,7 +71274,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -71372,81 +71283,173 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O383" t="n">
-        <v>7</v>
-      </c>
-      <c r="R383" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S383" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P383" t="n">
+        <v>2</v>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF383" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG383" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH383" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI383" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ383" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK383" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM383" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN383" t="b">
+        <v>0</v>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR383" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ383" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT383" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71478,12 +71481,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -71517,93 +71520,81 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="O384" t="n">
-        <v>103</v>
-      </c>
-      <c r="P384" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="R384" t="n">
-        <v>1.744063727749959</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA384" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO384" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ384" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS384" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR384" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr"/>
       <c r="AT384" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV384" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA384" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB384" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC384" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71630,7 +71621,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -71682,98 +71673,18 @@
       <c r="P385" t="n">
         <v>103</v>
       </c>
-      <c r="U385" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V385" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W385" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X385" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y385" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z385" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R385" t="n">
+        <v>1.744063727749959</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB385" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC385" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD385" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE385" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF385" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG385" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH385" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI385" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ385" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK385" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM385" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN385" t="b">
-        <v>1</v>
       </c>
       <c r="AO385" t="inlineStr">
         <is>
@@ -71911,106 +71822,106 @@
         </is>
       </c>
       <c r="N386" t="n">
+        <v>103</v>
+      </c>
+      <c r="O386" t="n">
+        <v>103</v>
+      </c>
+      <c r="P386" t="n">
+        <v>103</v>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF386" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ386" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK386" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM386" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN386" t="b">
         <v>1</v>
-      </c>
-      <c r="O386" t="n">
-        <v>1</v>
-      </c>
-      <c r="P386" t="n">
-        <v>1</v>
-      </c>
-      <c r="U386" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V386" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W386" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X386" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y386" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z386" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA386" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB386" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC386" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD386" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE386" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF386" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG386" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH386" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI386" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ386" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK386" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM386" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN386" t="b">
-        <v>0</v>
       </c>
       <c r="AO386" t="inlineStr">
         <is>
@@ -72104,17 +72015,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -72139,7 +72050,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -72148,81 +72059,173 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O387" t="n">
-        <v>8</v>
-      </c>
-      <c r="R387" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S387" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P387" t="n">
+        <v>1</v>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE387" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF387" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG387" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH387" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI387" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ387" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK387" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM387" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN387" t="b">
+        <v>0</v>
       </c>
       <c r="AO387" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP387" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR387" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS387" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ387" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT387" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU387" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV387" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA387" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB387" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC387" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -72254,12 +72257,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -72293,93 +72296,81 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="O388" t="n">
-        <v>88</v>
-      </c>
-      <c r="P388" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="R388" t="n">
-        <v>1.490073864485402</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S388" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA388" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO388" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP388" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ388" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS388" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR388" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr"/>
       <c r="AT388" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU388" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV388" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ388" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA388" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB388" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC388" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -72406,7 +72397,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -72458,98 +72449,18 @@
       <c r="P389" t="n">
         <v>88</v>
       </c>
-      <c r="U389" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W389" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X389" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y389" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z389" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R389" t="n">
+        <v>1.490073864485402</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC389" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD389" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE389" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF389" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG389" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH389" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI389" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ389" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK389" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM389" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN389" t="b">
-        <v>1</v>
       </c>
       <c r="AO389" t="inlineStr">
         <is>
@@ -72687,22 +72598,22 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="O390" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="P390" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="U390" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="V390" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="W390" t="inlineStr">
@@ -72712,7 +72623,7 @@
       </c>
       <c r="X390" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="Y390" t="inlineStr">
@@ -72747,7 +72658,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -72786,7 +72697,7 @@
         </is>
       </c>
       <c r="AN390" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO390" t="inlineStr">
         <is>
@@ -72880,17 +72791,17 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -72915,7 +72826,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -72924,81 +72835,173 @@
         </is>
       </c>
       <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0</v>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC391" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD391" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE391" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF391" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG391" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH391" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI391" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ391" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK391" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM391" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN391" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO391" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP391" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ391" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT391" t="n">
         <v>4</v>
       </c>
-      <c r="O391" t="n">
-        <v>4</v>
-      </c>
-      <c r="R391" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S391" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO391" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP391" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR391" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS391" t="inlineStr"/>
-      <c r="AT391" t="n">
-        <v>0</v>
-      </c>
       <c r="AU391" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV391" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ391" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA391" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB391" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC391" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73030,12 +73033,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -73060,22 +73063,22 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N392" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O392" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R392" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
@@ -73108,42 +73111,42 @@
       </c>
       <c r="AV392" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA392" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB392" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC392" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -73175,12 +73178,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -73205,36 +73208,34 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N393" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O393" t="n">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="P393" t="n">
+        <v>86</v>
       </c>
       <c r="R393" t="n">
-        <v>0</v>
+        <v>1.456208549383461</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
       <c r="AA393" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO393" t="inlineStr">
@@ -73244,70 +73245,65 @@
       </c>
       <c r="AP393" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ393" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR393" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS393" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1910</t>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
         </is>
       </c>
       <c r="AT393" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU393" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV393" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY393" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ393" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA393" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB393" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC393" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73339,12 +73335,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -73369,33 +73365,36 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N394" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O394" t="n">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="P394" t="n">
+        <v>86</v>
       </c>
       <c r="U394" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1910</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="V394" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1910</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="W394" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X394" t="inlineStr">
@@ -73410,12 +73409,12 @@
       </c>
       <c r="Z394" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB394" t="inlineStr">
@@ -73425,7 +73424,7 @@
       </c>
       <c r="AC394" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD394" t="inlineStr">
@@ -73460,12 +73459,12 @@
       </c>
       <c r="AJ394" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK394" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM394" t="inlineStr">
@@ -73483,70 +73482,65 @@
       </c>
       <c r="AP394" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ394" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR394" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS394" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1910</t>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
         </is>
       </c>
       <c r="AT394" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU394" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV394" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA394" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB394" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC394" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73573,17 +73567,17 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -73608,90 +73602,182 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N395" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O395" t="n">
-        <v>7</v>
-      </c>
-      <c r="R395" t="n">
-        <v>0.01356578946654432</v>
-      </c>
-      <c r="S395" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P395" t="n">
+        <v>1</v>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC395" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD395" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE395" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF395" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG395" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH395" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI395" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ395" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK395" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM395" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN395" t="b">
+        <v>0</v>
       </c>
       <c r="AO395" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP395" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR395" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS395" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ395" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT395" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU395" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV395" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ395" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA395" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB395" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC395" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73723,12 +73809,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -73762,100 +73848,81 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R396" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA396" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO396" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP396" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ396" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR396" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS396" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS396" t="inlineStr"/>
       <c r="AT396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU396" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV396" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ396" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA396" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB396" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC396" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -73882,217 +73949,1074 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>4484</v>
+      </c>
+      <c r="O397" t="n">
+        <v>4484</v>
+      </c>
+      <c r="R397" t="n">
+        <v>2.099617912384513</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO397" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP397" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR397" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS397" t="inlineStr"/>
+      <c r="AT397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU397" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV397" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW397" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX397" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY397" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA397" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB397" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC397" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N398" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0</v>
+      </c>
+      <c r="R398" t="n">
+        <v>0</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO398" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP398" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ398" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR398" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS398" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AT398" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU398" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV398" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW398" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX398" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY398" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA398" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB398" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC398" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr">
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N399" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" t="n">
+        <v>0</v>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB399" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC399" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD399" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE399" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF399" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG399" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI399" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ399" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK399" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM399" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN399" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO399" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP399" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ399" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR399" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS399" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AT399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU399" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV399" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW399" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX399" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY399" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA399" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB399" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC399" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>7</v>
+      </c>
+      <c r="O400" t="n">
+        <v>7</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0.01356578946654432</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR400" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS400" t="inlineStr"/>
+      <c r="AT400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU400" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV400" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW400" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX400" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY400" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA400" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB400" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC400" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
+      <c r="G401" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>D021</t>
-        </is>
-      </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="J397" t="inlineStr">
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
         <is>
           <t>登革热</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr">
+      <c r="K401" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
+      <c r="L401" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr">
+      <c r="M401" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N397" t="n">
+      <c r="N401" t="n">
         <v>1</v>
       </c>
-      <c r="O397" t="n">
+      <c r="O401" t="n">
         <v>1</v>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="R401" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V397" t="inlineStr">
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO401" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP401" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ401" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR401" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS401" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="W397" t="inlineStr">
+      <c r="AT401" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU401" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV401" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW401" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX401" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY401" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA401" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB401" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC401" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>1</v>
+      </c>
+      <c r="O402" t="n">
+        <v>1</v>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X397" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>Denguefeber</t>
         </is>
       </c>
-      <c r="Y397" t="inlineStr">
+      <c r="Y402" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z397" t="inlineStr">
+      <c r="Z402" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA397" t="inlineStr">
+      <c r="AA402" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB397" t="inlineStr">
+      <c r="AB402" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC397" t="inlineStr">
+      <c r="AC402" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD397" t="inlineStr">
+      <c r="AD402" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE397" t="inlineStr">
+      <c r="AE402" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF397" t="inlineStr">
+      <c r="AF402" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG397" t="inlineStr">
+      <c r="AG402" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH397" t="inlineStr">
+      <c r="AH402" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI397" t="inlineStr">
+      <c r="AI402" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ397" t="inlineStr">
+      <c r="AJ402" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK397" t="inlineStr">
+      <c r="AK402" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM397" t="inlineStr">
+      <c r="AM402" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN397" t="b">
+      <c r="AN402" t="b">
         <v>1</v>
       </c>
-      <c r="AO397" t="inlineStr">
+      <c r="AO402" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP397" t="inlineStr">
+      <c r="AP402" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ397" t="inlineStr">
+      <c r="AQ402" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR397" t="inlineStr">
+      <c r="AR402" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS397" t="inlineStr">
+      <c r="AS402" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="AT397" t="n">
+      <c r="AT402" t="n">
         <v>2</v>
       </c>
-      <c r="AU397" t="inlineStr">
+      <c r="AU402" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV397" t="inlineStr">
+      <c r="AV402" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW397" t="inlineStr">
+      <c r="AW402" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX397" t="inlineStr">
+      <c r="AX402" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY397" t="inlineStr">
+      <c r="AY402" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ397" t="inlineStr">
+      <c r="AZ402" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA397" t="inlineStr">
+      <c r="BA402" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB397" t="inlineStr">
+      <c r="BB402" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC397" t="inlineStr">
+      <c r="BC402" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -74214,7 +75138,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -74224,7 +75148,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11">
@@ -74244,7 +75168,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -74276,7 +75200,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>482817</v>
+        <v>489634</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -67037,13 +67037,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O358" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="R358" t="n">
-        <v>0.209350273712628</v>
+        <v>0.2240415209907072</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -74541,13 +74541,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O400" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R400" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -75200,7 +75200,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>489634</v>
+        <v>489643</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -67037,13 +67037,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O358" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R358" t="n">
-        <v>0.2240415209907072</v>
+        <v>0.227714332810227</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -75200,7 +75200,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>489643</v>
+        <v>489644</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -68872,13 +68872,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O370" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R370" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -74541,13 +74541,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O400" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R400" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -75019,6 +75019,151 @@
       <c r="BC402" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>6</v>
+      </c>
+      <c r="O403" t="n">
+        <v>6</v>
+      </c>
+      <c r="R403" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO403" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP403" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR403" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS403" t="inlineStr"/>
+      <c r="AT403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU403" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV403" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW403" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX403" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY403" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA403" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB403" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC403" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -75055,7 +75200,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -75138,7 +75283,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -75148,7 +75293,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11">
@@ -75200,7 +75345,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>489644</v>
+        <v>489650</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -62847,13 +62847,13 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O336" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R336" t="n">
-        <v>0.1891260466471829</v>
+        <v>0.1513008373177463</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
@@ -63006,10 +63006,10 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O337" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U337" t="inlineStr">
         <is>
@@ -69381,12 +69381,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -69420,13 +69420,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O373" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R373" t="n">
-        <v>0.03737952171313338</v>
+        <v>0.1134756279883097</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
@@ -69435,7 +69435,7 @@
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -69450,7 +69450,7 @@
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ373" t="inlineStr">
@@ -69458,62 +69458,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR373" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS373" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AT373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69545,12 +69540,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -69584,29 +69579,29 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O374" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U374" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="V374" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X374" t="inlineStr">
         <is>
-          <t>Denguefeber</t>
+          <t>Dengue fever</t>
         </is>
       </c>
       <c r="Y374" t="inlineStr">
@@ -69616,7 +69611,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -69631,7 +69626,7 @@
       </c>
       <c r="AC374" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD374" t="inlineStr">
@@ -69666,17 +69661,17 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly dengue notifications.</t>
         </is>
       </c>
       <c r="AM374" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN374" t="b">
@@ -69689,7 +69684,7 @@
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ374" t="inlineStr">
@@ -69697,62 +69692,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR374" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS374" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AT374" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69784,12 +69774,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -69823,81 +69813,100 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O375" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R375" t="n">
-        <v>0.05214830935724275</v>
+        <v>0.03737952171313338</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ375" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR375" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -69924,17 +69933,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -69959,7 +69968,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -69968,81 +69977,175 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O376" t="n">
-        <v>3</v>
-      </c>
-      <c r="R376" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK376" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM376" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN376" t="b">
+        <v>1</v>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ376" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR376" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS376" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -70074,12 +70177,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -70104,7 +70207,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -70113,93 +70216,81 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="O377" t="n">
-        <v>100</v>
-      </c>
-      <c r="P377" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="R377" t="n">
-        <v>1.693265755097047</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA377" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO377" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ377" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr"/>
       <c r="AT377" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -70226,17 +70317,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -70270,173 +70361,81 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="O378" t="n">
-        <v>100</v>
-      </c>
-      <c r="P378" t="n">
-        <v>100</v>
-      </c>
-      <c r="U378" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W378" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X378" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y378" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z378" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA378" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB378" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC378" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD378" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE378" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF378" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG378" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH378" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI378" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ378" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK378" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM378" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN378" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO378" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ378" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr"/>
       <c r="AT378" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70463,7 +70462,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -70507,106 +70506,26 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O379" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="P379" t="n">
-        <v>1</v>
-      </c>
-      <c r="U379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W379" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X379" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y379" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>100</v>
+      </c>
+      <c r="R379" t="n">
+        <v>1.693265755097047</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB379" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC379" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD379" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE379" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF379" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG379" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH379" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI379" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ379" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK379" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM379" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN379" t="b">
-        <v>0</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
@@ -70700,17 +70619,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -70735,7 +70654,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -70744,81 +70663,173 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="O380" t="n">
-        <v>8</v>
-      </c>
-      <c r="R380" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S380" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="P380" t="n">
+        <v>100</v>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF380" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ380" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK380" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM380" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN380" t="b">
+        <v>1</v>
       </c>
       <c r="AO380" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR380" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS380" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ380" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT380" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70845,7 +70856,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -70880,7 +70891,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -70889,26 +70900,106 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="O381" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="P381" t="n">
-        <v>93</v>
-      </c>
-      <c r="R381" t="n">
-        <v>1.574737152240254</v>
-      </c>
-      <c r="S381" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF381" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG381" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ381" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK381" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM381" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN381" t="b">
+        <v>0</v>
       </c>
       <c r="AO381" t="inlineStr">
         <is>
@@ -71002,17 +71093,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -71046,173 +71137,81 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="O382" t="n">
-        <v>93</v>
-      </c>
-      <c r="P382" t="n">
-        <v>93</v>
-      </c>
-      <c r="U382" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V382" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W382" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X382" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y382" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z382" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA382" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB382" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC382" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD382" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE382" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF382" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG382" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH382" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI382" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ382" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK382" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM382" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN382" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP382" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ382" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS382" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR382" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr"/>
       <c r="AT382" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU382" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV382" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA382" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB382" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC382" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71239,7 +71238,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -71283,106 +71282,26 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="O383" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="P383" t="n">
-        <v>2</v>
-      </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W383" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X383" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y383" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z383" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>93</v>
+      </c>
+      <c r="R383" t="n">
+        <v>1.574737152240254</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB383" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC383" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD383" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE383" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF383" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG383" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH383" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI383" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ383" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK383" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM383" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN383" t="b">
-        <v>0</v>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
@@ -71476,17 +71395,17 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -71511,7 +71430,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -71520,81 +71439,173 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="O384" t="n">
-        <v>7</v>
-      </c>
-      <c r="R384" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S384" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>93</v>
+      </c>
+      <c r="P384" t="n">
+        <v>93</v>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE384" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF384" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG384" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH384" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI384" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ384" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK384" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM384" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN384" t="b">
+        <v>1</v>
       </c>
       <c r="AO384" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR384" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS384" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ384" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT384" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV384" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA384" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB384" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC384" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71621,7 +71632,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -71656,7 +71667,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -71665,26 +71676,106 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="O385" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="P385" t="n">
-        <v>103</v>
-      </c>
-      <c r="R385" t="n">
-        <v>1.744063727749959</v>
-      </c>
-      <c r="S385" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF385" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG385" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH385" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI385" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ385" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK385" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM385" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN385" t="b">
+        <v>0</v>
       </c>
       <c r="AO385" t="inlineStr">
         <is>
@@ -71778,17 +71869,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -71822,173 +71913,81 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="O386" t="n">
-        <v>103</v>
-      </c>
-      <c r="P386" t="n">
-        <v>103</v>
-      </c>
-      <c r="U386" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V386" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W386" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X386" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y386" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z386" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA386" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB386" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC386" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD386" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE386" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF386" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG386" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH386" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI386" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ386" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK386" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM386" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN386" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO386" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP386" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ386" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS386" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR386" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr"/>
       <c r="AT386" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU386" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV386" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA386" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB386" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC386" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -72015,7 +72014,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -72059,106 +72058,26 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="O387" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="P387" t="n">
-        <v>1</v>
-      </c>
-      <c r="U387" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V387" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W387" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X387" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y387" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z387" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>103</v>
+      </c>
+      <c r="R387" t="n">
+        <v>1.744063727749959</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB387" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC387" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD387" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE387" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF387" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG387" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH387" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI387" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ387" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK387" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM387" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN387" t="b">
-        <v>0</v>
       </c>
       <c r="AO387" t="inlineStr">
         <is>
@@ -72252,17 +72171,17 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -72287,7 +72206,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -72296,81 +72215,173 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="O388" t="n">
-        <v>8</v>
-      </c>
-      <c r="R388" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S388" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="P388" t="n">
+        <v>103</v>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD388" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE388" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF388" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG388" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH388" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI388" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ388" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK388" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM388" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN388" t="b">
+        <v>1</v>
       </c>
       <c r="AO388" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP388" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR388" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS388" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ388" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT388" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU388" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV388" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ388" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA388" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB388" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC388" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -72397,7 +72408,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -72432,7 +72443,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -72441,26 +72452,106 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="O389" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="P389" t="n">
-        <v>88</v>
-      </c>
-      <c r="R389" t="n">
-        <v>1.490073864485402</v>
-      </c>
-      <c r="S389" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF389" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ389" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK389" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM389" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN389" t="b">
+        <v>0</v>
       </c>
       <c r="AO389" t="inlineStr">
         <is>
@@ -72554,17 +72645,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -72598,173 +72689,81 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="O390" t="n">
-        <v>88</v>
-      </c>
-      <c r="P390" t="n">
-        <v>88</v>
-      </c>
-      <c r="U390" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V390" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W390" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X390" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y390" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z390" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA390" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB390" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC390" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD390" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE390" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF390" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG390" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH390" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI390" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ390" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK390" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM390" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN390" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R390" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO390" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP390" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ390" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS390" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR390" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr"/>
       <c r="AT390" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU390" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV390" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA390" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB390" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC390" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -72791,7 +72790,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -72835,106 +72834,26 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="O391" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="P391" t="n">
-        <v>0</v>
-      </c>
-      <c r="U391" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V391" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W391" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X391" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y391" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z391" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>88</v>
+      </c>
+      <c r="R391" t="n">
+        <v>1.490073864485402</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB391" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC391" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD391" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE391" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF391" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG391" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH391" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI391" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ391" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK391" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM391" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN391" t="b">
-        <v>0</v>
       </c>
       <c r="AO391" t="inlineStr">
         <is>
@@ -73028,17 +72947,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -73063,7 +72982,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -73072,81 +72991,173 @@
         </is>
       </c>
       <c r="N392" t="n">
+        <v>88</v>
+      </c>
+      <c r="O392" t="n">
+        <v>88</v>
+      </c>
+      <c r="P392" t="n">
+        <v>88</v>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE392" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF392" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG392" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH392" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI392" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ392" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK392" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM392" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN392" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO392" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP392" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ392" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT392" t="n">
         <v>4</v>
       </c>
-      <c r="O392" t="n">
-        <v>4</v>
-      </c>
-      <c r="R392" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S392" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO392" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP392" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR392" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS392" t="inlineStr"/>
-      <c r="AT392" t="n">
-        <v>0</v>
-      </c>
       <c r="AU392" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV392" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA392" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB392" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC392" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73173,7 +73184,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -73208,7 +73219,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -73217,26 +73228,106 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="O393" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="P393" t="n">
-        <v>86</v>
-      </c>
-      <c r="R393" t="n">
-        <v>1.456208549383461</v>
-      </c>
-      <c r="S393" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB393" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC393" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD393" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE393" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF393" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG393" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH393" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI393" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ393" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK393" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM393" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN393" t="b">
+        <v>0</v>
       </c>
       <c r="AO393" t="inlineStr">
         <is>
@@ -73330,17 +73421,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -73374,173 +73465,81 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="O394" t="n">
-        <v>86</v>
-      </c>
-      <c r="P394" t="n">
-        <v>86</v>
-      </c>
-      <c r="U394" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V394" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W394" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X394" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y394" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z394" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA394" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB394" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC394" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD394" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE394" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF394" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG394" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH394" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI394" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ394" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK394" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM394" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN394" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R394" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO394" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP394" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ394" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS394" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR394" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr"/>
       <c r="AT394" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU394" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV394" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA394" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB394" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC394" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -73567,7 +73566,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -73611,106 +73610,26 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="O395" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="P395" t="n">
-        <v>1</v>
-      </c>
-      <c r="U395" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V395" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W395" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X395" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y395" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z395" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>86</v>
+      </c>
+      <c r="R395" t="n">
+        <v>1.456208549383461</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB395" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC395" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD395" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE395" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF395" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG395" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH395" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI395" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ395" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK395" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM395" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN395" t="b">
-        <v>0</v>
       </c>
       <c r="AO395" t="inlineStr">
         <is>
@@ -73804,17 +73723,17 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -73839,90 +73758,182 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N396" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O396" t="n">
-        <v>0</v>
-      </c>
-      <c r="R396" t="n">
-        <v>0</v>
-      </c>
-      <c r="S396" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>86</v>
+      </c>
+      <c r="P396" t="n">
+        <v>86</v>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG396" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI396" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ396" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK396" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM396" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN396" t="b">
+        <v>1</v>
       </c>
       <c r="AO396" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP396" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR396" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS396" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ396" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS396" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT396" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU396" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV396" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ396" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA396" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB396" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC396" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73949,17 +73960,17 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -73984,90 +73995,182 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N397" t="n">
-        <v>4484</v>
+        <v>1</v>
       </c>
       <c r="O397" t="n">
-        <v>4484</v>
-      </c>
-      <c r="R397" t="n">
-        <v>2.099617912384513</v>
-      </c>
-      <c r="S397" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P397" t="n">
+        <v>1</v>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC397" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD397" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE397" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF397" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG397" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH397" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI397" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ397" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK397" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM397" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN397" t="b">
+        <v>0</v>
       </c>
       <c r="AO397" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP397" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR397" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS397" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ397" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS397" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT397" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU397" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV397" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW397" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY397" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ397" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA397" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB397" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC397" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -74099,12 +74202,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -74151,87 +74254,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA398" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO398" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP398" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ398" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR398" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS398" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS398" t="inlineStr"/>
       <c r="AT398" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU398" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV398" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW398" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ398" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA398" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB398" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC398" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -74258,17 +74342,17 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -74302,175 +74386,81 @@
         </is>
       </c>
       <c r="N399" t="n">
+        <v>4484</v>
+      </c>
+      <c r="O399" t="n">
+        <v>4484</v>
+      </c>
+      <c r="R399" t="n">
+        <v>2.099617912384513</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO399" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP399" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR399" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS399" t="inlineStr"/>
+      <c r="AT399" t="n">
         <v>0</v>
       </c>
-      <c r="O399" t="n">
-        <v>0</v>
-      </c>
-      <c r="U399" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="V399" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W399" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X399" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y399" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z399" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA399" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB399" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC399" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD399" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE399" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF399" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG399" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH399" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI399" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ399" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK399" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM399" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN399" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO399" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP399" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ399" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR399" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS399" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AT399" t="n">
-        <v>2</v>
-      </c>
       <c r="AU399" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV399" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW399" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ399" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA399" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB399" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC399" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -74502,12 +74492,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -74541,81 +74531,100 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O400" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R400" t="n">
-        <v>0.0251936090092966</v>
+        <v>0</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP400" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ400" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR400" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS400" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS400" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU400" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV400" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ400" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA400" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB400" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC400" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -74642,17 +74651,17 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -74686,29 +74695,104 @@
         </is>
       </c>
       <c r="N401" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB401" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC401" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD401" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE401" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF401" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG401" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH401" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI401" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ401" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK401" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM401" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN401" t="b">
         <v>1</v>
       </c>
-      <c r="O401" t="n">
-        <v>1</v>
-      </c>
-      <c r="R401" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S401" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U401" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA401" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO401" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -74721,7 +74805,7 @@
       </c>
       <c r="AQ401" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR401" t="inlineStr">
@@ -74731,7 +74815,7 @@
       </c>
       <c r="AS401" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
       <c r="AT401" t="n">
@@ -74739,47 +74823,47 @@
       </c>
       <c r="AU401" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV401" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW401" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ401" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA401" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB401" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC401" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -74806,17 +74890,17 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -74850,175 +74934,81 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O402" t="n">
-        <v>1</v>
-      </c>
-      <c r="U402" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V402" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W402" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X402" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y402" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z402" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA402" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB402" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC402" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD402" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE402" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF402" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG402" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH402" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI402" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ402" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK402" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM402" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN402" t="b">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="R402" t="n">
+        <v>0.0251936090092966</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO402" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP402" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ402" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR402" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS402" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS402" t="inlineStr"/>
       <c r="AT402" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU402" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV402" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW402" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ402" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA402" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB402" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC402" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -75050,118 +75040,521 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>1</v>
+      </c>
+      <c r="O403" t="n">
+        <v>1</v>
+      </c>
+      <c r="R403" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO403" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP403" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ403" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR403" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS403" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU403" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV403" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW403" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX403" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY403" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA403" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB403" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC403" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>1</v>
+      </c>
+      <c r="O404" t="n">
+        <v>1</v>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB404" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC404" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD404" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE404" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF404" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG404" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH404" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI404" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ404" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK404" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM404" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN404" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO404" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP404" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ404" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR404" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS404" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT404" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU404" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV404" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW404" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX404" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY404" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA404" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB404" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC404" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr">
+      <c r="G405" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>D021</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
         <is>
           <t>登革热</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr">
+      <c r="K405" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L403" t="inlineStr">
+      <c r="L405" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr">
+      <c r="M405" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N403" t="n">
+      <c r="N405" t="n">
         <v>6</v>
       </c>
-      <c r="O403" t="n">
+      <c r="O405" t="n">
         <v>6</v>
       </c>
-      <c r="R403" t="n">
+      <c r="R405" t="n">
         <v>0.004900850445394598</v>
       </c>
-      <c r="S403" t="inlineStr">
+      <c r="S405" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO403" t="inlineStr">
+      <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP403" t="inlineStr">
+      <c r="AP405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR403" t="inlineStr">
+      <c r="AR405" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS403" t="inlineStr"/>
-      <c r="AT403" t="n">
+      <c r="AS405" t="inlineStr"/>
+      <c r="AT405" t="n">
         <v>0</v>
       </c>
-      <c r="AU403" t="inlineStr">
+      <c r="AU405" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV403" t="inlineStr">
+      <c r="AV405" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW403" t="inlineStr">
+      <c r="AW405" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX403" t="inlineStr">
+      <c r="AX405" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY403" t="inlineStr">
+      <c r="AY405" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ403" t="inlineStr">
+      <c r="AZ405" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA403" t="inlineStr">
+      <c r="BA405" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB403" t="inlineStr">
+      <c r="BB405" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC403" t="inlineStr">
+      <c r="BC405" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -75283,7 +75676,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -75293,7 +75686,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11">
@@ -75313,7 +75706,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -75345,7 +75738,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>489650</v>
+        <v>489654</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -75079,13 +75079,13 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R403" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
@@ -75243,10 +75243,10 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -75738,7 +75738,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>489654</v>
+        <v>489655</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -58378,13 +58378,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>41466</v>
+        <v>40512</v>
       </c>
       <c r="O312" t="n">
-        <v>41466</v>
+        <v>40512</v>
       </c>
       <c r="R312" t="n">
-        <v>19.41631497656918</v>
+        <v>18.96960768655696</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -68176,13 +68176,13 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>39979</v>
+        <v>38015</v>
       </c>
       <c r="O366" t="n">
-        <v>39979</v>
+        <v>38015</v>
       </c>
       <c r="R366" t="n">
-        <v>18.7200322299778</v>
+        <v>17.8003958383803</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -74386,13 +74386,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>4484</v>
+        <v>11319</v>
       </c>
       <c r="O399" t="n">
-        <v>4484</v>
+        <v>11319</v>
       </c>
       <c r="R399" t="n">
-        <v>2.099617912384513</v>
+        <v>5.300083664201673</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -75738,7 +75738,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>489655</v>
+        <v>493572</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -67037,13 +67037,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O358" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R358" t="n">
-        <v>0.227714332810227</v>
+        <v>0.2387327682687863</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -74934,13 +74934,13 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O402" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R402" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S402" t="inlineStr">
         <is>
@@ -75557,6 +75557,637 @@
       <c r="BC405" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>72</v>
+      </c>
+      <c r="O406" t="n">
+        <v>72</v>
+      </c>
+      <c r="P406" t="n">
+        <v>72</v>
+      </c>
+      <c r="R406" t="n">
+        <v>1.219151343669874</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO406" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP406" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ406" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS406" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT406" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU406" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV406" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW406" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX406" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY406" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA406" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB406" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC406" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>72</v>
+      </c>
+      <c r="O407" t="n">
+        <v>72</v>
+      </c>
+      <c r="P407" t="n">
+        <v>72</v>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB407" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC407" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD407" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE407" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF407" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG407" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH407" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI407" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ407" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK407" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM407" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN407" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO407" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP407" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ407" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS407" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT407" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU407" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV407" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW407" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX407" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY407" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA407" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB407" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC407" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>1</v>
+      </c>
+      <c r="O408" t="n">
+        <v>1</v>
+      </c>
+      <c r="P408" t="n">
+        <v>1</v>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD408" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE408" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF408" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG408" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH408" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI408" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ408" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK408" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM408" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN408" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO408" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP408" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ408" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT408" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU408" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV408" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW408" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX408" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY408" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA408" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB408" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC408" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -75676,7 +76307,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -75686,7 +76317,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11">
@@ -75706,7 +76337,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -75738,7 +76369,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>493572</v>
+        <v>493650</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -74934,13 +74934,13 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O402" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R402" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S402" t="inlineStr">
         <is>
@@ -76369,7 +76369,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>493650</v>
+        <v>493651</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -57239,13 +57239,13 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O304" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R304" t="n">
-        <v>0.3929908646886175</v>
+        <v>0.3966636765081373</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -58378,13 +58378,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>40512</v>
+        <v>39691</v>
       </c>
       <c r="O312" t="n">
-        <v>40512</v>
+        <v>39691</v>
       </c>
       <c r="R312" t="n">
-        <v>18.96960768655696</v>
+        <v>18.58517719903071</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -68176,13 +68176,13 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>38015</v>
+        <v>35953</v>
       </c>
       <c r="O366" t="n">
-        <v>38015</v>
+        <v>35953</v>
       </c>
       <c r="R366" t="n">
-        <v>17.8003958383803</v>
+        <v>16.83487127652997</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -68833,12 +68833,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -68872,13 +68872,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O370" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R370" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -68911,42 +68911,42 @@
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -68978,12 +68978,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -69017,100 +69017,81 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O371" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R371" t="n">
-        <v>0.2122770990954608</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA371" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO371" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ371" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR371" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS371" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr"/>
       <c r="AT371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -69137,7 +69118,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -69186,98 +69167,23 @@
       <c r="O372" t="n">
         <v>12</v>
       </c>
+      <c r="R372" t="n">
+        <v>0.2122770990954608</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U372" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W372" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X372" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y372" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA372" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB372" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC372" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD372" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE372" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF372" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG372" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH372" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI372" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ372" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK372" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM372" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN372" t="b">
-        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
@@ -69376,17 +69282,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -69420,22 +69326,39 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O373" t="n">
-        <v>6</v>
-      </c>
-      <c r="R373" t="n">
-        <v>0.1134756279883097</v>
-      </c>
-      <c r="S373" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>SER_NZ_DENGUE_MONTHLY</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -69443,6 +69366,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ373" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK373" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM373" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN373" t="b">
+        <v>1</v>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69450,7 +69431,7 @@
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ373" t="inlineStr">
@@ -69458,57 +69439,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS373" t="inlineStr">
         <is>
-          <t>SER_NZ_DENGUE_MONTHLY</t>
+          <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
       <c r="AT373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -69535,7 +69521,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -69584,98 +69570,23 @@
       <c r="O374" t="n">
         <v>6</v>
       </c>
+      <c r="R374" t="n">
+        <v>0.1134756279883097</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U374" t="inlineStr">
         <is>
           <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>SER_NZ_DENGUE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W374" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X374" t="inlineStr">
-        <is>
-          <t>Dengue fever</t>
-        </is>
-      </c>
-      <c r="Y374" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA374" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC374" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD374" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE374" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF374" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG374" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH374" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI374" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ374" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK374" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly dengue notifications.</t>
-        </is>
-      </c>
-      <c r="AM374" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN374" t="b">
-        <v>1</v>
       </c>
       <c r="AO374" t="inlineStr">
         <is>
@@ -69769,17 +69680,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -69813,22 +69724,39 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O375" t="n">
-        <v>4</v>
-      </c>
-      <c r="R375" t="n">
-        <v>0.03737952171313338</v>
-      </c>
-      <c r="S375" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U375" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>Dengue fever</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -69836,6 +69764,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF375" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG375" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ375" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK375" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly dengue notifications.</t>
+        </is>
+      </c>
+      <c r="AM375" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN375" t="b">
+        <v>1</v>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69843,7 +69829,7 @@
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ375" t="inlineStr">
@@ -69851,62 +69837,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR375" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS375" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+          <t>SER_NZ_DENGUE_MONTHLY</t>
         </is>
       </c>
       <c r="AT375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69933,7 +69914,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -69982,98 +69963,23 @@
       <c r="O376" t="n">
         <v>4</v>
       </c>
+      <c r="R376" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U376" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DENGUE</t>
         </is>
       </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_DENGUE</t>
-        </is>
-      </c>
-      <c r="W376" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X376" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y376" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA376" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB376" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC376" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD376" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE376" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF376" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG376" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH376" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI376" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ376" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK376" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM376" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN376" t="b">
-        <v>1</v>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
@@ -70172,17 +70078,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -70216,81 +70122,175 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O377" t="n">
-        <v>12</v>
-      </c>
-      <c r="R377" t="n">
-        <v>0.05214830935724275</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ377" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK377" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM377" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN377" t="b">
+        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ377" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR377" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS377" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DENGUE</t>
+        </is>
+      </c>
       <c r="AT377" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -70322,12 +70322,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -70352,7 +70352,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -70361,13 +70361,13 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O378" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R378" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -70400,42 +70400,42 @@
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -70467,12 +70467,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -70506,93 +70506,81 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="O379" t="n">
-        <v>100</v>
-      </c>
-      <c r="P379" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="R379" t="n">
-        <v>1.693265755097047</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA379" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO379" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP379" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ379" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR379" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS379" t="inlineStr"/>
       <c r="AT379" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70619,7 +70607,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -70671,98 +70659,18 @@
       <c r="P380" t="n">
         <v>100</v>
       </c>
-      <c r="U380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W380" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X380" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y380" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z380" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R380" t="n">
+        <v>1.693265755097047</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB380" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC380" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD380" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE380" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF380" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG380" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH380" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI380" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ380" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK380" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM380" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN380" t="b">
-        <v>1</v>
       </c>
       <c r="AO380" t="inlineStr">
         <is>
@@ -70900,106 +70808,106 @@
         </is>
       </c>
       <c r="N381" t="n">
+        <v>100</v>
+      </c>
+      <c r="O381" t="n">
+        <v>100</v>
+      </c>
+      <c r="P381" t="n">
+        <v>100</v>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF381" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG381" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ381" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK381" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM381" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN381" t="b">
         <v>1</v>
-      </c>
-      <c r="O381" t="n">
-        <v>1</v>
-      </c>
-      <c r="P381" t="n">
-        <v>1</v>
-      </c>
-      <c r="U381" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V381" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W381" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X381" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y381" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z381" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA381" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB381" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC381" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD381" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE381" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF381" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG381" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH381" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI381" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ381" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK381" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM381" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN381" t="b">
-        <v>0</v>
       </c>
       <c r="AO381" t="inlineStr">
         <is>
@@ -71093,17 +71001,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -71128,7 +71036,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -71137,81 +71045,173 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O382" t="n">
-        <v>8</v>
-      </c>
-      <c r="R382" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P382" t="n">
+        <v>1</v>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF382" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG382" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH382" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI382" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ382" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK382" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM382" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN382" t="b">
+        <v>0</v>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP382" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR382" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS382" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ382" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT382" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU382" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV382" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA382" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB382" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC382" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71243,12 +71243,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -71282,93 +71282,81 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="O383" t="n">
-        <v>93</v>
-      </c>
-      <c r="P383" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="R383" t="n">
-        <v>1.574737152240254</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA383" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ383" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr"/>
       <c r="AT383" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71395,7 +71383,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -71447,98 +71435,18 @@
       <c r="P384" t="n">
         <v>93</v>
       </c>
-      <c r="U384" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V384" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W384" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X384" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y384" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z384" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R384" t="n">
+        <v>1.574737152240254</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB384" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC384" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD384" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE384" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF384" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG384" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH384" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI384" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ384" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK384" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM384" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN384" t="b">
-        <v>1</v>
       </c>
       <c r="AO384" t="inlineStr">
         <is>
@@ -71676,22 +71584,22 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="O385" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="P385" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="U385" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="V385" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="W385" t="inlineStr">
@@ -71701,7 +71609,7 @@
       </c>
       <c r="X385" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="Y385" t="inlineStr">
@@ -71736,7 +71644,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -71775,7 +71683,7 @@
         </is>
       </c>
       <c r="AN385" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO385" t="inlineStr">
         <is>
@@ -71869,17 +71777,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -71904,7 +71812,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -71913,81 +71821,173 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O386" t="n">
-        <v>7</v>
-      </c>
-      <c r="R386" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S386" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P386" t="n">
+        <v>2</v>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF386" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ386" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK386" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM386" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN386" t="b">
+        <v>0</v>
       </c>
       <c r="AO386" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP386" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR386" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS386" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ386" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT386" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU386" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV386" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA386" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB386" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC386" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -72019,12 +72019,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -72058,93 +72058,81 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="O387" t="n">
-        <v>103</v>
-      </c>
-      <c r="P387" t="n">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="R387" t="n">
-        <v>1.744063727749959</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA387" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO387" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP387" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ387" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS387" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR387" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr"/>
       <c r="AT387" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU387" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV387" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA387" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB387" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC387" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -72171,7 +72159,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -72223,98 +72211,18 @@
       <c r="P388" t="n">
         <v>103</v>
       </c>
-      <c r="U388" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V388" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W388" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X388" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y388" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z388" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R388" t="n">
+        <v>1.744063727749959</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB388" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC388" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD388" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE388" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF388" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG388" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH388" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI388" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ388" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK388" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM388" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN388" t="b">
-        <v>1</v>
       </c>
       <c r="AO388" t="inlineStr">
         <is>
@@ -72452,106 +72360,106 @@
         </is>
       </c>
       <c r="N389" t="n">
+        <v>103</v>
+      </c>
+      <c r="O389" t="n">
+        <v>103</v>
+      </c>
+      <c r="P389" t="n">
+        <v>103</v>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF389" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ389" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK389" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM389" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN389" t="b">
         <v>1</v>
-      </c>
-      <c r="O389" t="n">
-        <v>1</v>
-      </c>
-      <c r="P389" t="n">
-        <v>1</v>
-      </c>
-      <c r="U389" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W389" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X389" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y389" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z389" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA389" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC389" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD389" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE389" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF389" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG389" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH389" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI389" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ389" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK389" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM389" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN389" t="b">
-        <v>0</v>
       </c>
       <c r="AO389" t="inlineStr">
         <is>
@@ -72645,17 +72553,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -72680,7 +72588,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -72689,81 +72597,173 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O390" t="n">
-        <v>8</v>
-      </c>
-      <c r="R390" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S390" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P390" t="n">
+        <v>1</v>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE390" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF390" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG390" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH390" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI390" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ390" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK390" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM390" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN390" t="b">
+        <v>0</v>
       </c>
       <c r="AO390" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP390" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR390" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS390" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ390" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT390" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU390" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV390" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA390" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB390" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC390" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -72795,12 +72795,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -72834,93 +72834,81 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="O391" t="n">
-        <v>88</v>
-      </c>
-      <c r="P391" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="R391" t="n">
-        <v>1.490073864485402</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S391" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA391" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO391" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP391" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ391" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS391" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR391" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr"/>
       <c r="AT391" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU391" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV391" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW391" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ391" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA391" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB391" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC391" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -72947,7 +72935,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -72999,98 +72987,18 @@
       <c r="P392" t="n">
         <v>88</v>
       </c>
-      <c r="U392" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V392" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W392" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X392" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y392" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z392" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R392" t="n">
+        <v>1.490073864485402</v>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB392" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC392" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD392" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE392" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF392" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG392" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH392" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI392" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ392" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK392" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM392" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN392" t="b">
-        <v>1</v>
       </c>
       <c r="AO392" t="inlineStr">
         <is>
@@ -73228,22 +73136,22 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="O393" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="P393" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="U393" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="V393" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+          <t>SER_SG_CDA_DENGUE</t>
         </is>
       </c>
       <c r="W393" t="inlineStr">
@@ -73253,7 +73161,7 @@
       </c>
       <c r="X393" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="Y393" t="inlineStr">
@@ -73288,7 +73196,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -73327,7 +73235,7 @@
         </is>
       </c>
       <c r="AN393" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO393" t="inlineStr">
         <is>
@@ -73421,17 +73329,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -73456,7 +73364,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -73465,81 +73373,173 @@
         </is>
       </c>
       <c r="N394" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0</v>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF394" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG394" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH394" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI394" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ394" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK394" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM394" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN394" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO394" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP394" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ394" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT394" t="n">
         <v>4</v>
       </c>
-      <c r="O394" t="n">
-        <v>4</v>
-      </c>
-      <c r="R394" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S394" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO394" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP394" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR394" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS394" t="inlineStr"/>
-      <c r="AT394" t="n">
-        <v>0</v>
-      </c>
       <c r="AU394" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV394" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA394" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB394" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC394" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -73571,12 +73571,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -73610,93 +73610,81 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="O395" t="n">
-        <v>86</v>
-      </c>
-      <c r="P395" t="n">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="R395" t="n">
-        <v>1.456208549383461</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S395" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA395" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO395" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP395" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ395" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS395" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR395" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr"/>
       <c r="AT395" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU395" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV395" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ395" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA395" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB395" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC395" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -73723,7 +73711,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -73775,98 +73763,18 @@
       <c r="P396" t="n">
         <v>86</v>
       </c>
-      <c r="U396" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V396" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W396" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X396" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y396" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z396" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R396" t="n">
+        <v>1.456208549383461</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB396" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC396" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD396" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE396" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF396" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG396" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH396" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI396" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ396" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK396" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM396" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN396" t="b">
-        <v>1</v>
       </c>
       <c r="AO396" t="inlineStr">
         <is>
@@ -74004,106 +73912,106 @@
         </is>
       </c>
       <c r="N397" t="n">
+        <v>86</v>
+      </c>
+      <c r="O397" t="n">
+        <v>86</v>
+      </c>
+      <c r="P397" t="n">
+        <v>86</v>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC397" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD397" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE397" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF397" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG397" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH397" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI397" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ397" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK397" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM397" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN397" t="b">
         <v>1</v>
-      </c>
-      <c r="O397" t="n">
-        <v>1</v>
-      </c>
-      <c r="P397" t="n">
-        <v>1</v>
-      </c>
-      <c r="U397" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V397" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W397" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X397" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y397" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z397" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA397" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB397" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC397" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD397" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE397" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF397" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG397" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH397" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI397" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ397" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK397" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM397" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN397" t="b">
-        <v>0</v>
       </c>
       <c r="AO397" t="inlineStr">
         <is>
@@ -74197,17 +74105,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -74232,90 +74140,182 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N398" t="n">
+        <v>1</v>
+      </c>
+      <c r="O398" t="n">
+        <v>1</v>
+      </c>
+      <c r="P398" t="n">
+        <v>1</v>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB398" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC398" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD398" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE398" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF398" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG398" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH398" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI398" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ398" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK398" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM398" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN398" t="b">
         <v>0</v>
       </c>
-      <c r="O398" t="n">
-        <v>0</v>
-      </c>
-      <c r="R398" t="n">
-        <v>0</v>
-      </c>
-      <c r="S398" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO398" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP398" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR398" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS398" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ398" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS398" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
       <c r="AT398" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU398" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV398" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW398" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ398" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA398" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB398" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC398" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -74347,12 +74347,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -74386,13 +74386,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>11319</v>
+        <v>0</v>
       </c>
       <c r="O399" t="n">
-        <v>11319</v>
+        <v>0</v>
       </c>
       <c r="R399" t="n">
-        <v>5.300083664201673</v>
+        <v>0</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -74425,42 +74425,42 @@
       </c>
       <c r="AV399" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW399" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ399" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA399" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB399" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC399" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -74492,12 +74492,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -74531,100 +74531,81 @@
         </is>
       </c>
       <c r="N400" t="n">
+        <v>19662</v>
+      </c>
+      <c r="O400" t="n">
+        <v>19662</v>
+      </c>
+      <c r="R400" t="n">
+        <v>9.20666534195011</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR400" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS400" t="inlineStr"/>
+      <c r="AT400" t="n">
         <v>0</v>
       </c>
-      <c r="O400" t="n">
-        <v>0</v>
-      </c>
-      <c r="R400" t="n">
-        <v>0</v>
-      </c>
-      <c r="S400" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U400" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AA400" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO400" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP400" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ400" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR400" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS400" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="AT400" t="n">
-        <v>2</v>
-      </c>
       <c r="AU400" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV400" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ400" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA400" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB400" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC400" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -74651,7 +74632,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -74700,98 +74681,23 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
+      <c r="R401" t="n">
+        <v>0</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U401" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1910</t>
         </is>
       </c>
-      <c r="V401" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1910</t>
-        </is>
-      </c>
-      <c r="W401" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X401" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y401" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z401" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA401" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB401" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC401" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD401" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE401" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF401" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG401" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH401" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI401" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ401" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK401" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
-        </is>
-      </c>
-      <c r="AM401" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN401" t="b">
-        <v>1</v>
       </c>
       <c r="AO401" t="inlineStr">
         <is>
@@ -74890,17 +74796,17 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -74934,81 +74840,175 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O402" t="n">
-        <v>17</v>
-      </c>
-      <c r="R402" t="n">
-        <v>0.03294548870446478</v>
-      </c>
-      <c r="S402" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB402" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC402" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD402" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE402" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF402" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG402" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH402" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI402" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ402" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK402" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM402" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN402" t="b">
+        <v>1</v>
       </c>
       <c r="AO402" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP402" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ402" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR402" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS402" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS402" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
       <c r="AT402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU402" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV402" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW402" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ402" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA402" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB402" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC402" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -75040,12 +75040,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -75079,100 +75079,81 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O403" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R403" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA403" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO403" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP403" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ403" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR403" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS403" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS403" t="inlineStr"/>
       <c r="AT403" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU403" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV403" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW403" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ403" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA403" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB403" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC403" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -75199,7 +75180,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -75243,103 +75224,28 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O404" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="R404" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U404" t="inlineStr">
         <is>
           <t>SER_NO_FHI_510_MONTHLY</t>
         </is>
       </c>
-      <c r="V404" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_510_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W404" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X404" t="inlineStr">
-        <is>
-          <t>Denguefeber</t>
-        </is>
-      </c>
-      <c r="Y404" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z404" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA404" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB404" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC404" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD404" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE404" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF404" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG404" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH404" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI404" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ404" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK404" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM404" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN404" t="b">
-        <v>1</v>
       </c>
       <c r="AO404" t="inlineStr">
         <is>
@@ -75438,17 +75344,17 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -75473,7 +75379,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -75482,81 +75388,175 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O405" t="n">
-        <v>6</v>
-      </c>
-      <c r="R405" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S405" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>Denguefeber</t>
+        </is>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB405" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC405" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD405" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE405" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF405" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG405" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH405" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI405" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ405" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK405" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM405" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN405" t="b">
+        <v>1</v>
       </c>
       <c r="AO405" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP405" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ405" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR405" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS405" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS405" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_510_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT405" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU405" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV405" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW405" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ405" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA405" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB405" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC405" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -75588,12 +75588,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -75627,93 +75627,81 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="O406" t="n">
-        <v>72</v>
-      </c>
-      <c r="P406" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="R406" t="n">
-        <v>1.219151343669874</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA406" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO406" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP406" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ406" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS406" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR406" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS406" t="inlineStr"/>
       <c r="AT406" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU406" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV406" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW406" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA406" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB406" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC406" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -75740,7 +75728,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -75792,98 +75780,18 @@
       <c r="P407" t="n">
         <v>72</v>
       </c>
-      <c r="U407" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="V407" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE</t>
-        </is>
-      </c>
-      <c r="W407" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X407" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="Y407" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z407" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R407" t="n">
+        <v>1.219151343669874</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA407" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB407" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC407" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD407" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE407" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF407" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG407" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH407" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI407" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ407" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK407" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM407" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN407" t="b">
-        <v>1</v>
       </c>
       <c r="AO407" t="inlineStr">
         <is>
@@ -76021,106 +75929,106 @@
         </is>
       </c>
       <c r="N408" t="n">
+        <v>72</v>
+      </c>
+      <c r="O408" t="n">
+        <v>72</v>
+      </c>
+      <c r="P408" t="n">
+        <v>72</v>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD408" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE408" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF408" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG408" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH408" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI408" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ408" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK408" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM408" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN408" t="b">
         <v>1</v>
-      </c>
-      <c r="O408" t="n">
-        <v>1</v>
-      </c>
-      <c r="P408" t="n">
-        <v>1</v>
-      </c>
-      <c r="U408" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="V408" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
-        </is>
-      </c>
-      <c r="W408" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X408" t="inlineStr">
-        <is>
-          <t>DHF</t>
-        </is>
-      </c>
-      <c r="Y408" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z408" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA408" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB408" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC408" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD408" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE408" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF408" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG408" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH408" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI408" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ408" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK408" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM408" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN408" t="b">
-        <v>0</v>
       </c>
       <c r="AO408" t="inlineStr">
         <is>
@@ -76186,6 +76094,1019 @@
         </is>
       </c>
       <c r="BC408" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>1</v>
+      </c>
+      <c r="O409" t="n">
+        <v>1</v>
+      </c>
+      <c r="P409" t="n">
+        <v>1</v>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC409" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD409" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE409" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF409" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG409" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH409" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI409" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ409" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK409" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM409" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN409" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO409" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP409" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ409" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT409" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU409" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV409" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW409" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX409" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY409" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA409" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB409" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC409" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>5</v>
+      </c>
+      <c r="O410" t="n">
+        <v>5</v>
+      </c>
+      <c r="R410" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO410" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP410" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR410" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS410" t="inlineStr"/>
+      <c r="AT410" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU410" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV410" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW410" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX410" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY410" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA410" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB410" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC410" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>74</v>
+      </c>
+      <c r="O411" t="n">
+        <v>74</v>
+      </c>
+      <c r="P411" t="n">
+        <v>74</v>
+      </c>
+      <c r="R411" t="n">
+        <v>1.253016658771815</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO411" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP411" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ411" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS411" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT411" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU411" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV411" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW411" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX411" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY411" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA411" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB411" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC411" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>74</v>
+      </c>
+      <c r="O412" t="n">
+        <v>74</v>
+      </c>
+      <c r="P412" t="n">
+        <v>74</v>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB412" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC412" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD412" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE412" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF412" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG412" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH412" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI412" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ412" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK412" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM412" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN412" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO412" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP412" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ412" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT412" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU412" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV412" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW412" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX412" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY412" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA412" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB412" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC412" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB413" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC413" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD413" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE413" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF413" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG413" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH413" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI413" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ413" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK413" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM413" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN413" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO413" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP413" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ413" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT413" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU413" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV413" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW413" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX413" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY413" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA413" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB413" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC413" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -76224,7 +77145,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -76307,7 +77228,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -76317,7 +77238,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11">
@@ -76337,7 +77258,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -76369,7 +77290,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>493651</v>
+        <v>499196</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -67422,13 +67422,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="O360" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R360" t="n">
-        <v>0.2387327682687863</v>
+        <v>0.2497512037273457</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -68561,13 +68561,13 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>35953</v>
+        <v>34742</v>
       </c>
       <c r="O368" t="n">
-        <v>35953</v>
+        <v>34742</v>
       </c>
       <c r="R368" t="n">
-        <v>16.83487127652997</v>
+        <v>16.26782460126288</v>
       </c>
       <c r="S368" t="inlineStr">
         <is>
@@ -73038,13 +73038,13 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R392" t="n">
-        <v>0.03737952171313338</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
@@ -73202,10 +73202,10 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U393" t="inlineStr">
         <is>
@@ -77466,13 +77466,13 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O415" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R415" t="n">
-        <v>0</v>
+        <v>0.1505852846003114</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
@@ -77611,13 +77611,13 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>19662</v>
+        <v>27095</v>
       </c>
       <c r="O416" t="n">
-        <v>19662</v>
+        <v>27095</v>
       </c>
       <c r="R416" t="n">
-        <v>9.20666534195011</v>
+        <v>12.68714258163657</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -77756,13 +77756,13 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R417" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S417" t="inlineStr">
         <is>
@@ -77920,10 +77920,10 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U418" t="inlineStr">
         <is>
@@ -78159,13 +78159,13 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O419" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R419" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.04069736839963296</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
@@ -80189,6 +80189,1330 @@
       <c r="BC429" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>9</v>
+      </c>
+      <c r="O430" t="n">
+        <v>9</v>
+      </c>
+      <c r="R430" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR430" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr"/>
+      <c r="AT430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU430" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV430" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW430" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX430" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY430" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA430" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB430" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC430" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>82</v>
+      </c>
+      <c r="O431" t="n">
+        <v>82</v>
+      </c>
+      <c r="P431" t="n">
+        <v>82</v>
+      </c>
+      <c r="R431" t="n">
+        <v>1.388477919179579</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO431" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP431" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ431" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS431" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT431" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU431" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV431" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW431" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX431" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY431" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA431" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB431" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC431" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N432" t="n">
+        <v>82</v>
+      </c>
+      <c r="O432" t="n">
+        <v>82</v>
+      </c>
+      <c r="P432" t="n">
+        <v>82</v>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE</t>
+        </is>
+      </c>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB432" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC432" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD432" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE432" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF432" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG432" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH432" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI432" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ432" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK432" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM432" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN432" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO432" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP432" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ432" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT432" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU432" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV432" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW432" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX432" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY432" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA432" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB432" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC432" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N433" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE_HAEMORRHAGIC_FEVER</t>
+        </is>
+      </c>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>DHF</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB433" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC433" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD433" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE433" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF433" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG433" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH433" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI433" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ433" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK433" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM433" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN433" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO433" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP433" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ433" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS433" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DENGUE; SER_SG_HIST_DENGUE</t>
+        </is>
+      </c>
+      <c r="AT433" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU433" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV433" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW433" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX433" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY433" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA433" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB433" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC433" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="R434" t="n">
+        <v>0</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO434" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP434" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ434" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR434" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS434" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AT434" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU434" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV434" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW434" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX434" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY434" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA434" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB434" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC434" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="W435" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB435" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC435" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD435" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE435" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF435" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG435" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH435" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI435" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ435" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK435" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1910.</t>
+        </is>
+      </c>
+      <c r="AM435" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN435" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO435" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP435" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ435" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR435" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS435" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1910</t>
+        </is>
+      </c>
+      <c r="AT435" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU435" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV435" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW435" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX435" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY435" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA435" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB435" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC435" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+      <c r="R436" t="n">
+        <v>0</v>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO436" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP436" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR436" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr"/>
+      <c r="AT436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU436" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV436" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW436" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX436" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY436" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA436" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB436" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC436" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -80225,7 +81549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -80308,7 +81632,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -80318,7 +81642,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11">
@@ -80338,7 +81662,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -80370,7 +81694,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>499468</v>
+        <v>505828</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -67422,13 +67422,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O360" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="R360" t="n">
-        <v>0.2497512037273457</v>
+        <v>0.2570968273663853</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -77466,13 +77466,13 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O415" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R415" t="n">
-        <v>0.1505852846003114</v>
+        <v>0.157930908239351</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
@@ -81694,7 +81694,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>505828</v>
+        <v>505832</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d021/2026-2029.xlsx
+++ b/diseases/d021/2026-2029.xlsx
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -33257,7 +33257,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -42458,7 +42458,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -53047,7 +53047,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -63085,7 +63085,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -72498,7 +72498,7 @@
       </c>
       <c r="AM389" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN389" t="b">
@@ -78304,13 +78304,13 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O420" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R420" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
@@ -78468,10 +78468,10 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O421" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U421" t="inlineStr">
         <is>
@@ -78560,7 +78560,7 @@
       </c>
       <c r="AM421" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN421" t="b">
@@ -81694,7 +81694,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>505832</v>
+        <v>505834</v>
       </c>
     </row>
     <row r="16">
